--- a/output/0 - profiler/document_inventory.xlsx
+++ b/output/0 - profiler/document_inventory.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Document Inventory'!$A$1:$AE$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Document Inventory'!$A$1:$AE$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1174,8 +1174,602 @@
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Incident_Response_example demo-2026-003 copy.docx</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>4225</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>909</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Appendix A - Incident Response Plan Temp</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>Table-heavy: 50.7% table content (threshold: 40%)</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>7232</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1412</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Section 4 - Log Management Controls</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>Table-heavy: 42.0% table content (threshold: 40%)</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>4287</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>996</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Appendix B - Email Content Inspection Ru</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>Table-heavy: 61.7% table content (threshold: 40%)</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4199</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>993</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Appendix F - Third-Party Risk Assessment</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>Table-heavy: 69.5% table content (threshold: 40%)</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>8628</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1518</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Appendix A - Key Lifecycle Management Pr</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid: 23.7% table content, 2 procedure keywords detected</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>10046</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1806</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Appendix A - Privacy Impact Assessment R</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid: 24.8% table content, 2 procedure keywords detected</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE6"/>
+  <autoFilter ref="A1:AE12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1200,7 +1794,7 @@
         </is>
       </c>
       <c r="B1" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2">
@@ -1214,7 +1808,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1828,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1278,7 +1872,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1298,7 +1892,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1342,7 +1936,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>2765</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="18">
@@ -1352,7 +1946,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>710</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="19">
@@ -1362,7 +1956,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>3552</v>
+        <v>11186</v>
       </c>
     </row>
     <row r="20">
@@ -1372,7 +1966,7 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="21">
@@ -1382,7 +1976,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="22">
@@ -1392,7 +1986,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -1402,7 +1996,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -1412,7 +2006,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/output/0 - profiler/document_inventory.xlsx
+++ b/output/0 - profiler/document_inventory.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Document Inventory'!$A$1:$AE$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Document Inventory'!$A$1:$AN$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,7 +48,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
         <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,6 +127,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -490,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE12"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -522,8 +531,17 @@
     <col width="8" customWidth="1" min="27" max="27"/>
     <col width="8" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="45" customWidth="1" min="30" max="30"/>
-    <col width="30" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col width="8" customWidth="1" min="33" max="33"/>
+    <col width="7" customWidth="1" min="34" max="34"/>
+    <col width="30" customWidth="1" min="35" max="35"/>
+    <col width="8" customWidth="1" min="36" max="36"/>
+    <col width="45" customWidth="1" min="37" max="37"/>
+    <col width="30" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -674,12 +692,57 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
+          <t>Control IDs</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Ctrls/Page</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Control Dense</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Heading Variance</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Level Skips</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Unique Sections</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Table Dense</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>Type Reason</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Errors</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Term: AC</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Term: Cloud</t>
         </is>
       </c>
     </row>
@@ -775,12 +838,41 @@
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr"/>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>Configuration Management Policy, Section 3: Roles and Respon</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AK2" s="4" t="inlineStr">
         <is>
           <t>Table-heavy: 254.0% table content (threshold: 40%)</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr"/>
+      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AN2" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -874,12 +966,37 @@
       <c r="AA3" s="2" t="inlineStr"/>
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr"/>
-      <c r="AD3" s="2" t="inlineStr">
+      <c r="AD3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>Access Control Policy, 4. Enforcement</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AK3" s="4" t="inlineStr">
         <is>
           <t>Table-heavy: 129.0% table content (threshold: 40%)</t>
         </is>
       </c>
-      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -969,12 +1086,39 @@
       <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
-      <c r="AD4" s="2" t="inlineStr">
+      <c r="AD4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>Risk Management Framework Compliance Mapping, Revision Histo</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AK4" s="4" t="inlineStr">
         <is>
           <t>Table-heavy: 252.5% table content (threshold: 40%)</t>
         </is>
       </c>
-      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AL4" s="2" t="inlineStr"/>
+      <c r="AM4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN4" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1068,12 +1212,37 @@
       <c r="AA5" s="2" t="inlineStr"/>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
-      <c r="AD5" s="2" t="inlineStr">
+      <c r="AD5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>Incident Response Policy, 1.1 Policy Rationale, 4.3 Escalati</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AK5" s="4" t="inlineStr">
         <is>
           <t>Table-heavy: 50.2% table content (threshold: 40%)</t>
         </is>
       </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1084,7 +1253,7 @@
           <t>Acceptable_Use_Policy_POL-AU-2026-006.docx</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1167,12 +1336,35 @@
       <c r="AA6" s="2" t="inlineStr"/>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
-      <c r="AD6" s="2" t="inlineStr">
+      <c r="AD6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable Use Policy, Email and Communications, 6. Enforcem</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr">
         <is>
           <t>Hybrid: low table content (6.6%) but 2 procedure keywords detected</t>
         </is>
       </c>
-      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1266,12 +1458,43 @@
       <c r="AA7" s="2" t="inlineStr"/>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
-      <c r="AD7" s="2" t="inlineStr">
+      <c r="AD7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="2" t="inlineStr">
+        <is>
+          <t>Incident Response Policy, Enforcement</t>
+        </is>
+      </c>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AK7" s="4" t="inlineStr">
         <is>
           <t>Table-heavy: 50.7% table content (threshold: 40%)</t>
         </is>
       </c>
-      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1365,12 +1588,45 @@
       <c r="AA8" s="2" t="inlineStr"/>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
-      <c r="AD8" s="2" t="inlineStr">
+      <c r="AD8" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG8" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI8" s="2" t="inlineStr">
+        <is>
+          <t>Continuous Monitoring Policy, Enforcement</t>
+        </is>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AK8" s="4" t="inlineStr">
         <is>
           <t>Table-heavy: 42.0% table content (threshold: 40%)</t>
         </is>
       </c>
-      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1464,12 +1720,47 @@
       <c r="AA9" s="2" t="inlineStr"/>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
-      <c r="AD9" s="2" t="inlineStr">
+      <c r="AD9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE9" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="2" t="inlineStr">
+        <is>
+          <t>Data Loss Prevention Standard, Enforcement</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AK9" s="4" t="inlineStr">
         <is>
           <t>Table-heavy: 61.7% table content (threshold: 40%)</t>
         </is>
       </c>
-      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1563,12 +1854,41 @@
       <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr"/>
-      <c r="AD10" s="2" t="inlineStr">
+      <c r="AD10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>Risk Management Policy, Enforcement</t>
+        </is>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AK10" s="4" t="inlineStr">
         <is>
           <t>Table-heavy: 69.5% table content (threshold: 40%)</t>
         </is>
       </c>
-      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1579,7 +1899,7 @@
           <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1662,12 +1982,41 @@
       <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr"/>
-      <c r="AD11" s="2" t="inlineStr">
+      <c r="AD11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG11" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI11" s="2" t="inlineStr">
+        <is>
+          <t>Encryption Policy, Enforcement</t>
+        </is>
+      </c>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr">
         <is>
           <t>Hybrid: 23.7% table content, 2 procedure keywords detected</t>
         </is>
       </c>
-      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1678,7 +2027,7 @@
           <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1761,15 +2110,42 @@
       <c r="AA12" s="2" t="inlineStr"/>
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr"/>
-      <c r="AD12" s="2" t="inlineStr">
+      <c r="AD12" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG12" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>Privacy and PII Handling Policy, Enforcement</t>
+        </is>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr">
         <is>
           <t>Hybrid: 24.8% table content, 2 procedure keywords detected</t>
         </is>
       </c>
-      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE12"/>
+  <autoFilter ref="A1:AN12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1780,7 +2156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1788,224 +2164,278 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Total Documents</t>
         </is>
       </c>
-      <c r="B1" s="7" t="n">
+      <c r="B1" s="8" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr"/>
-      <c r="B2" s="7" t="inlineStr"/>
+      <c r="A2" s="7" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Type A (Table-Heavy)</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="8" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Type B (Prose-Heavy)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Type C (Hybrid)</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Type D (Appendix-Dominant)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Type E (Unclassified)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
-      <c r="B8" s="7" t="inlineStr"/>
+      <c r="A8" s="7" t="inlineStr"/>
+      <c r="B8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Over 36k Character Limit</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Has Fake Headings</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="8" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Has Merged Cell Tables</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Has Cross-References</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="8" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Has Tracked Changes</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Has Comments</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Missing 1+ Standard Sections</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="7" t="inlineStr"/>
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Control Dense Docs</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Heading Variance Docs</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Table Dense Docs</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Docs with Unique Sections</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Avg Controls/Page</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Avg Characters</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B23" s="8" t="n">
         <v>4767</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Avg Words</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B24" s="8" t="n">
         <v>1017</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Total Words Across All Docs</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B25" s="8" t="n">
         <v>11186</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Avg Pages (approx)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B26" s="8" t="n">
         <v>1.4</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Avg Tables</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B27" s="8" t="n">
         <v>3.6</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Avg Cross-Refs</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B28" s="8" t="n">
         <v>2.7</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Total Tables Across All Docs</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B29" s="8" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Total Cross-Refs Across All Docs</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B30" s="8" t="n">
         <v>30</v>
       </c>
     </row>
